--- a/islami-assistant-web/public/data/الفروع.xlsx
+++ b/islami-assistant-web/public/data/الفروع.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BLACK-DIAMOND\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BLACK-DIAMOND\Desktop\islami Assistant\islami-assistant-web\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC6BF83-6B07-4D75-B448-1406158BF2E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D39B4C3-F737-4BA9-9127-4AD497525435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -342,7 +342,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="عادي" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -643,7 +643,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="31.5">
+    <row r="2" spans="1:4" ht="15.75">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -657,7 +657,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="47.25">
+    <row r="3" spans="1:4" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -671,7 +671,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="31.5">
+    <row r="4" spans="1:4" ht="15.75">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -685,7 +685,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="31.5">
+    <row r="5" spans="1:4" ht="15.75">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -697,7 +697,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="31.5">
+    <row r="6" spans="1:4" ht="15.75">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
@@ -711,7 +711,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="47.25">
+    <row r="7" spans="1:4" ht="15.75">
       <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
@@ -725,7 +725,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="31.5">
+    <row r="8" spans="1:4" ht="15.75">
       <c r="A8" s="1" t="s">
         <v>27</v>
       </c>
@@ -739,7 +739,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="47.25">
+    <row r="9" spans="1:4" ht="15.75">
       <c r="A9" s="1" t="s">
         <v>31</v>
       </c>
@@ -753,7 +753,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="31.5">
+    <row r="10" spans="1:4" ht="15.75">
       <c r="A10" s="1" t="s">
         <v>35</v>
       </c>
@@ -767,7 +767,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="47.25">
+    <row r="11" spans="1:4" ht="15.75">
       <c r="A11" s="1" t="s">
         <v>39</v>
       </c>
@@ -781,7 +781,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="31.5">
+    <row r="12" spans="1:4" ht="15.75">
       <c r="A12" s="1" t="s">
         <v>43</v>
       </c>
@@ -795,7 +795,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="47.25">
+    <row r="13" spans="1:4" ht="15.75">
       <c r="A13" s="1" t="s">
         <v>47</v>
       </c>
@@ -809,7 +809,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="47.25">
+    <row r="14" spans="1:4" ht="31.5">
       <c r="A14" s="1" t="s">
         <v>51</v>
       </c>
@@ -823,7 +823,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="47.25">
+    <row r="15" spans="1:4" ht="15.75">
       <c r="A15" s="1" t="s">
         <v>55</v>
       </c>
@@ -837,7 +837,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="47.25">
+    <row r="16" spans="1:4" ht="15.75">
       <c r="A16" s="1" t="s">
         <v>59</v>
       </c>
@@ -851,7 +851,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="31.5">
+    <row r="17" spans="1:4" ht="15.75">
       <c r="A17" s="1" t="s">
         <v>63</v>
       </c>
@@ -865,7 +865,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="31.5">
+    <row r="18" spans="1:4" ht="15.75">
       <c r="A18" s="1" t="s">
         <v>67</v>
       </c>
@@ -879,7 +879,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="31.5">
+    <row r="19" spans="1:4" ht="15.75">
       <c r="A19" s="1" t="s">
         <v>71</v>
       </c>
@@ -893,7 +893,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="31.5">
+    <row r="20" spans="1:4" ht="15.75">
       <c r="A20" s="1" t="s">
         <v>75</v>
       </c>
@@ -907,7 +907,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="31.5">
+    <row r="21" spans="1:4" ht="15.75">
       <c r="A21" s="1" t="s">
         <v>79</v>
       </c>

--- a/islami-assistant-web/public/data/الفروع.xlsx
+++ b/islami-assistant-web/public/data/الفروع.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BLACK-DIAMOND\Desktop\islami Assistant\islami-assistant-web\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D39B4C3-F737-4BA9-9127-4AD497525435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908663CE-DF91-4713-BFC1-0DFE519419E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3090" yWindow="4500" windowWidth="21600" windowHeight="10980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="298">
   <si>
     <t>الموقع</t>
   </si>
@@ -274,6 +275,651 @@
   </si>
   <si>
     <t>4428 خلدا 11953</t>
+  </si>
+  <si>
+    <t>مكتب عمان مول ( سي تاون )</t>
+  </si>
+  <si>
+    <t>تلاع العلي - شارع محمد فياض- عمان مول التجاري</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5007</t>
+  </si>
+  <si>
+    <t>جبل التّاج</t>
+  </si>
+  <si>
+    <t>جبل التّاج - شارع التّاج - قرب مسجد البقاعي شارع الحاووز</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5021</t>
+  </si>
+  <si>
+    <t>410676 الرمز البريدي 11141</t>
+  </si>
+  <si>
+    <t>فرع جبل عمان</t>
+  </si>
+  <si>
+    <t>جبل عمان - شارع البحتري - الدوار الثاني / فوق مطعم أبو جبارة</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5013</t>
+  </si>
+  <si>
+    <t>840610 الرمز البريدي 11180 عمان</t>
+  </si>
+  <si>
+    <t>فرع جبل النصر</t>
+  </si>
+  <si>
+    <t>جبل النصر - شارع السيدة هاجر - مقابل شركة أورانج</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5022</t>
+  </si>
+  <si>
+    <t>425838 الرمز البريدي 11140</t>
+  </si>
+  <si>
+    <t>فرع العبدلي مول</t>
+  </si>
+  <si>
+    <t>فرع العبدلي مول : محافظة العاصمة - منطقة العبدلي -شارع الاستثمار- مجمع العبدلي مول التجاري الطابق الثاني.</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5008</t>
+  </si>
+  <si>
+    <t>927988 الرمز البريدي 11190</t>
+  </si>
+  <si>
+    <t>فرع عمان</t>
+  </si>
+  <si>
+    <t>وسط البلد - شارع الملك حسين - قرب مجمع الفحيص التجاري</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5005</t>
+  </si>
+  <si>
+    <t>7987 الرمز البريدي 1118</t>
+  </si>
+  <si>
+    <t>فرع الهاشمي الشمالي</t>
+  </si>
+  <si>
+    <t>الهاشمية -شارع الهاشمي - مدخل مجمع سفريات بشرى - سال</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5017</t>
+  </si>
+  <si>
+    <t>230693 الرمز البريدي 11123</t>
+  </si>
+  <si>
+    <t>فرع الشميساني</t>
+  </si>
+  <si>
+    <t>الشميساني - شارع الثقافة - شارع 11 آب</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5002</t>
+  </si>
+  <si>
+    <t>925997 الرمز البريدي 11190</t>
+  </si>
+  <si>
+    <t>فرع عجلون - وسط البلد</t>
+  </si>
+  <si>
+    <t>عجلون - عجلون – عمان - وسط البلد 167 الرمز البريدي 26810 شاع الملك حسين</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5076</t>
+  </si>
+  <si>
+    <t>167 الرمز البريدي 26810</t>
+  </si>
+  <si>
+    <t>فرع عبين عبلين</t>
+  </si>
+  <si>
+    <t>عبين عبلين - شارع الملك حسين - مثلث اشتفينا</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5102</t>
+  </si>
+  <si>
+    <t>28عجلون 26833</t>
+  </si>
+  <si>
+    <t>فرع دير أبي سعيد</t>
+  </si>
+  <si>
+    <t>دير أبي سعيد - شارع الملك حسين - قرب الدوار الرئيسي مدخل المدينة</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5068</t>
+  </si>
+  <si>
+    <t>45 الرمز البريدي 21710</t>
+  </si>
+  <si>
+    <t>فرع اربد سيتى سنتر</t>
+  </si>
+  <si>
+    <t>وسط البلد - شارع الأمير حسن - المجمع التجاري "إربد سيتي سنتر"</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5101</t>
+  </si>
+  <si>
+    <t>1233 الرمز البريدي 21110</t>
+  </si>
+  <si>
+    <t>فرع اربد شارع الحصن</t>
+  </si>
+  <si>
+    <t>الحصن - الرئيسي - الحي الشرقي / بجانب المحكمة الشرعية شارع الحصن الرئيسي 357 الرمز البريدي 21510</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5063</t>
+  </si>
+  <si>
+    <t>357 الرمز البريدي 21510</t>
+  </si>
+  <si>
+    <t>فرع اربد شارع إيدون</t>
+  </si>
+  <si>
+    <t>الحي الجنوبي - شارع شفيق ارشيدات - إيدون / شمال إشارة الإسكان</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5060</t>
+  </si>
+  <si>
+    <t>620595 الرمز البريدي 21162</t>
+  </si>
+  <si>
+    <t>فرع اربد شارع حكما</t>
+  </si>
+  <si>
+    <t>الحي الشمالي - شارع حكما - مجمع سفريات الشمال</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5067</t>
+  </si>
+  <si>
+    <t>230101 الرمز البريدي 21110</t>
+  </si>
+  <si>
+    <t>فرع اربد شارع الهاشمي</t>
+  </si>
+  <si>
+    <t>الهاشمية - الهاشمي - مدخل مجمع سفريات بشرى - سال</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5065</t>
+  </si>
+  <si>
+    <t>501 الرمز البريدي 21101</t>
+  </si>
+  <si>
+    <t>فرع اربد شارع بغداد</t>
+  </si>
+  <si>
+    <t>وسط البلد - شارع بغداد - قرب شركة الكهرباء</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5073</t>
+  </si>
+  <si>
+    <t>1950 الرمز البريدي 21110</t>
+  </si>
+  <si>
+    <t>فرع عين الباشا</t>
+  </si>
+  <si>
+    <t>بلدية عين الباشا - مقابل كازية عين الباشا - قرب الاشارة الضوئية 77 الرمز البريدي 19384 شارع اليرموك</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5105</t>
+  </si>
+  <si>
+    <t>77 الرمز البريدي 19384</t>
+  </si>
+  <si>
+    <t>مكتب الصبيحي</t>
+  </si>
+  <si>
+    <t>الصبيحي - شارع أحمد عارف سعد المناصير - مقابل مسجد جعفر الطيّار.</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5036</t>
+  </si>
+  <si>
+    <t>484 السلط الرمز البريدي 19110 الأردن</t>
+  </si>
+  <si>
+    <t>فرع الشونة الجنوبية</t>
+  </si>
+  <si>
+    <t>الشونة الجنوبية - جسر الملك حسين - بجانب المؤسسة الاستهلاكية</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5037</t>
+  </si>
+  <si>
+    <t>23 الشونة الجنوبية 18110 الأردن</t>
+  </si>
+  <si>
+    <t>فرع دير علا</t>
+  </si>
+  <si>
+    <t>دير علا - شارع طريق وادي الأردن السريع - مقابل بلدية دير علا الجديدة</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5062</t>
+  </si>
+  <si>
+    <t>44 الرمز البريدي 18210</t>
+  </si>
+  <si>
+    <t>فرع بوابة السلط</t>
+  </si>
+  <si>
+    <t>السّلط - شارع الملك عبدالله الثاني - مقابل قصر العدل / مجمع فائق الدباس</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5090</t>
+  </si>
+  <si>
+    <t>484 السلط الرمز البريدي 19110الاردن</t>
+  </si>
+  <si>
+    <t>فرع السلط</t>
+  </si>
+  <si>
+    <t>السّلط - شارع البياضا - مبنى مؤسسة إعمار السّلط</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5078</t>
+  </si>
+  <si>
+    <t>1035 الرمز البريدي 19110</t>
+  </si>
+  <si>
+    <t>البقعة</t>
+  </si>
+  <si>
+    <t>مخيم البقعة -شارع جرش - مبنى جمعية المركز الإسلامي الخيرية</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5055</t>
+  </si>
+  <si>
+    <t>825 الرمز البريدي 19381</t>
+  </si>
+  <si>
+    <t>مكتب الحسا</t>
+  </si>
+  <si>
+    <t>لواء الحسا -شارع الطريق الصحراوي - بجانب المؤسسة الاستهلاكية العسكرية</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5104</t>
+  </si>
+  <si>
+    <t>55 الرمز البريدي 64610</t>
+  </si>
+  <si>
+    <t>مكتب بصيرا</t>
+  </si>
+  <si>
+    <t>لواء بصيرا - شارع عبد القادر الأسود - عند مدخل القرية</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5088</t>
+  </si>
+  <si>
+    <t>54 الرمز البريدي 66610</t>
+  </si>
+  <si>
+    <t>فرع الطفيلة</t>
+  </si>
+  <si>
+    <t>شارع الأمير زيد بن الحسين/ الطفيلة</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5080</t>
+  </si>
+  <si>
+    <t>42 الرمز البريدي 66110</t>
+  </si>
+  <si>
+    <t>فرع العقبة</t>
+  </si>
+  <si>
+    <t>حي الرضوان - شارع عرار - مجمع البنك الإسلامي</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5082</t>
+  </si>
+  <si>
+    <t>1048 الرمز البريدي 77110</t>
+  </si>
+  <si>
+    <t>مكتب جامعة العلوم الاسلامية العالمية</t>
+  </si>
+  <si>
+    <t>محافظة العاصمة منطقة طارق - شارع عبد العزيز الخياط - بجانب مسجد كلية الدعوة وأصول الدين</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5115</t>
+  </si>
+  <si>
+    <t>ص . ب 592 عمان 11947الأردن</t>
+  </si>
+  <si>
+    <t>فرع ضاحية الأمير حسن</t>
+  </si>
+  <si>
+    <t>شارع السلطان قلاوون -مقابل مجمع سرايا مول</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5114</t>
+  </si>
+  <si>
+    <t>212818 الرمز البريدي 11121 الأردن</t>
+  </si>
+  <si>
+    <t>فرع جبل الحسين</t>
+  </si>
+  <si>
+    <t>جبل الحسين - شارع خالد بن الوليد - مقابل مجمع عادل القاسم</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5006</t>
+  </si>
+  <si>
+    <t>926943 الرمز البريدي 11110</t>
+  </si>
+  <si>
+    <t>فرع شفا بدران</t>
+  </si>
+  <si>
+    <t>شارع عبدالله اللوزي بجانب بلدية الجبيهة</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5103</t>
+  </si>
+  <si>
+    <t>49 الرمز البريدي 11934</t>
+  </si>
+  <si>
+    <t>مكتب بافليون مول</t>
+  </si>
+  <si>
+    <t>ضاحية الياسمين - شارع الامير هاشم -مجمع بافيليون التجاري</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5113</t>
+  </si>
+  <si>
+    <t>710068 عمان 11117</t>
+  </si>
+  <si>
+    <t>فرع ضاحية الرشيد</t>
+  </si>
+  <si>
+    <t>ضاحية الرشيد - شارع عاكف الفايز - بجانب سكن أميمة بناية رقم (70)</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5111</t>
+  </si>
+  <si>
+    <t>96115 عمان 11196 الأردن</t>
+  </si>
+  <si>
+    <t>فرع عبدون</t>
+  </si>
+  <si>
+    <t>عبدون الشمالي - شارع فوزي القاوقجى -بناية رقم 5</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5106</t>
+  </si>
+  <si>
+    <t>852745 عمان - الأردن 11185</t>
+  </si>
+  <si>
+    <t>فرع المدينة الرياضية</t>
+  </si>
+  <si>
+    <t>المدينة الرياضية - شارع الملكة رانيا العبدالله - قرب ميدان الأمير زيد بن شاكر</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5046</t>
+  </si>
+  <si>
+    <t>19197 الرمز البريدي 11196</t>
+  </si>
+  <si>
+    <t>مكتب وادي السير</t>
+  </si>
+  <si>
+    <t>وادي السير - شارع عراق الأمير - حي وادي السير – باتجاه حي الميدان</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5045</t>
+  </si>
+  <si>
+    <t>140223 عمان - الأردن 11814</t>
+  </si>
+  <si>
+    <t>مكتب سامح مول</t>
+  </si>
+  <si>
+    <t>طبربور - شارع الشهيد (الأتوستراد) - داخل مجمع سامح مول (عريفة مول)</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5044</t>
+  </si>
+  <si>
+    <t>295 الرمز البريدي 11947</t>
+  </si>
+  <si>
+    <t>مكتب الاستقلال مول</t>
+  </si>
+  <si>
+    <t>جبل النزهة - شارع الاستقلال - داخل مجمع الاستقلال مول</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5015</t>
+  </si>
+  <si>
+    <t>922503 الرمز البريدي 11192</t>
+  </si>
+  <si>
+    <t>فرع صويلح</t>
+  </si>
+  <si>
+    <t>صويلح - شارع الاميرة راية</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5053</t>
+  </si>
+  <si>
+    <t>717 الرمز البريدي 11910</t>
+  </si>
+  <si>
+    <t>فرع سحاب</t>
+  </si>
+  <si>
+    <t>سحاب/ قرب سوق الخضار 647 الرمز البريدي 11511 شارع الأمير حسن</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5058</t>
+  </si>
+  <si>
+    <t>647 الرمز البريدي 11511</t>
+  </si>
+  <si>
+    <t>فرع شارع الحرية</t>
+  </si>
+  <si>
+    <t>المقابلين -شارع الحرية - مقابل محطة توتال للمحروقات</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5031</t>
+  </si>
+  <si>
+    <t>606 عمان- الأردن 11623</t>
+  </si>
+  <si>
+    <t>فرع خريبة السوق</t>
+  </si>
+  <si>
+    <t>خريبة السّوق - شارع الكفاح - مقابل مثلث جمعية المركز الإسلامي الخيرية</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5030</t>
+  </si>
+  <si>
+    <t>987 الرمز البريدي 11621 خريبة السوق</t>
+  </si>
+  <si>
+    <t>فرع ابو علندا</t>
+  </si>
+  <si>
+    <t>أبو علندا - شارع الحزام - مقابل مدينة أبو علندا الصناعية</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5066</t>
+  </si>
+  <si>
+    <t>742 الرمز البريدي 11592</t>
+  </si>
+  <si>
+    <t>فرع الجيزة</t>
+  </si>
+  <si>
+    <t>الجيزة - شارع الطريق الصحراوي - قرب مديرية تربية البادية</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5040</t>
+  </si>
+  <si>
+    <t>282 الرمز البريدي 16010</t>
+  </si>
+  <si>
+    <t>فرع ناعور</t>
+  </si>
+  <si>
+    <t>لواء ناعور - مأدبا الغربي - حي الشهيد - مجمع الساكت التجاري 114 الرمز البريدي 11710</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5028</t>
+  </si>
+  <si>
+    <t>114 الرمز البريدي 11710</t>
+  </si>
+  <si>
+    <t>فرع مرج الحمام</t>
+  </si>
+  <si>
+    <t>محافظة العاصمة - منطقة مرج الحمام -شارع الأميرة تغريد - دوار الاتصالات</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5026</t>
+  </si>
+  <si>
+    <t>1093 الرمز البريدي 11732</t>
+  </si>
+  <si>
+    <t>فرع ضاحية الياسمين</t>
+  </si>
+  <si>
+    <t>ضاحية الياسمين -شارع جبل عرفات - مجمع معتز الكسواني</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5029</t>
+  </si>
+  <si>
+    <t>710068 عمان - الأردن 11117</t>
+  </si>
+  <si>
+    <t>فرع حي نزال</t>
+  </si>
+  <si>
+    <t>حي نزّال - شارع الدستور - مقابل حلويات العنبتاوي</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5023</t>
+  </si>
+  <si>
+    <t>710999 الرمز البريدي 11171</t>
+  </si>
+  <si>
+    <t>فرع اليرموك</t>
+  </si>
+  <si>
+    <t>القويسمة - شارع اليرموك - قرب دوار الشرق الأوسط</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5025</t>
+  </si>
+  <si>
+    <t>620823 الرمز البريدي 11162</t>
+  </si>
+  <si>
+    <t>فرع الوحدات</t>
+  </si>
+  <si>
+    <t>مخيم الوحدات - مأدبا - مقابل مركز أمن الأشرفية دخلة حلويات الأفغاني 16165 الرمز البريدي 11152 شارع الامير حسن</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5020</t>
+  </si>
+  <si>
+    <t>16165 الرمز البريدي 11152</t>
+  </si>
+  <si>
+    <t>فرع المستشفى الاسلامي</t>
+  </si>
+  <si>
+    <t>العبدلي - شارع الملك حسين</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5014</t>
+  </si>
+  <si>
+    <t>928430 الرمز البريدي 11190</t>
+  </si>
+  <si>
+    <t>مكتب بلعما</t>
+  </si>
+  <si>
+    <t>بلعما - الرئيسي - بجانب مديرية قضاء بلعما - المفرق</t>
+  </si>
+  <si>
+    <t>+962 6 5670000 Ext. 5042</t>
+  </si>
+  <si>
+    <t>185 الرمز البريدي 13125</t>
+  </si>
+  <si>
+    <t>الادارة العامة</t>
+  </si>
+  <si>
+    <t>الشميساني- عمان - الأردن 11 اب شارع الثقافه</t>
+  </si>
+  <si>
+    <t>+96265670000 Ext. 5001</t>
+  </si>
+  <si>
+    <t>ص. ب 926225 عمان 11190 الأردن</t>
   </si>
 </sst>
 </file>
@@ -620,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.42578125" customWidth="1"/>
@@ -921,7 +1567,1212 @@
         <v>82</v>
       </c>
     </row>
+    <row r="22" spans="1:4" ht="15.75">
+      <c r="A22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75">
+      <c r="A23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.75">
+      <c r="A24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="31.5">
+      <c r="A25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.75">
+      <c r="A26" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.75">
+      <c r="A27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.75">
+      <c r="A28" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15.75">
+      <c r="A29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15.75">
+      <c r="A30" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15.75">
+      <c r="A31" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15.75">
+      <c r="A32" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15.75">
+      <c r="A33" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="31.5">
+      <c r="A34" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15.75">
+      <c r="A35" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="31.5">
+      <c r="A36" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.75">
+      <c r="A37" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15.75">
+      <c r="A38" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15.75">
+      <c r="A39" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="31.5">
+      <c r="A40" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15.75">
+      <c r="A41" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15.75">
+      <c r="A42" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15.75">
+      <c r="A43" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="31.5">
+      <c r="A44" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15.75">
+      <c r="A45" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15.75">
+      <c r="A46" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15.75">
+      <c r="A47" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15.75">
+      <c r="A48" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="31.5">
+      <c r="A49" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="31.5">
+      <c r="A50" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="31.5">
+      <c r="A51" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15.75">
+      <c r="A52" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="31.5">
+      <c r="A53" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15.75">
+      <c r="A54" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15.75">
+      <c r="A55" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="31.5">
+      <c r="A56" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15.75">
+      <c r="A57" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="15.75">
+      <c r="A58" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="15.75">
+      <c r="A59" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="31.5">
+      <c r="A60" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="31.5">
+      <c r="A61" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="15.75">
+      <c r="A62" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="15.75">
+      <c r="A63" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="15.75">
+      <c r="A64" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15.75">
+      <c r="A65" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="15.75">
+      <c r="A66" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="31.5">
+      <c r="A67" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="31.5">
+      <c r="A68" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="31.5">
+      <c r="A69" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="15.75">
+      <c r="A70" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15.75">
+      <c r="A71" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="15.75">
+      <c r="A72" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="15.75">
+      <c r="A73" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="15.75">
+      <c r="A74" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="31.5">
+      <c r="A75" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15.75">
+      <c r="A76" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="15.75">
+      <c r="A77" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="15.75">
+      <c r="A78" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="15.75">
+      <c r="A79" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="15.75">
+      <c r="A80" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="15.75">
+      <c r="A81" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15.75">
+      <c r="A82" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15.75">
+      <c r="A83" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="15.75">
+      <c r="A84" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15.75">
+      <c r="A85" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="31.5">
+      <c r="A86" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="15.75">
+      <c r="A87" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="15.75">
+      <c r="A88" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="31.5">
+      <c r="A89" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="15.75">
+      <c r="A90" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="31.5">
+      <c r="A91" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="15.75">
+      <c r="A92" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="15.75">
+      <c r="A93" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="31.5">
+      <c r="A94" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="31.5">
+      <c r="A95" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="15.75">
+      <c r="A96" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="31.5">
+      <c r="A97" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="15.75">
+      <c r="A98" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="15.75">
+      <c r="A99" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="15.75">
+      <c r="A100" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="15.75">
+      <c r="A101" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="15.75">
+      <c r="A102" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="15.75">
+      <c r="A103" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="31.5">
+      <c r="A104" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="15.75">
+      <c r="A105" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="31.5">
+      <c r="A106" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D70F4804-B638-4C42-B098-E21AB930A35C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="80.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/islami-assistant-web/public/data/الفروع.xlsx
+++ b/islami-assistant-web/public/data/الفروع.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BLACK-DIAMOND\Desktop\islami Assistant\islami-assistant-web\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908663CE-DF91-4713-BFC1-0DFE519419E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5975E0-AEDF-499F-9E75-29C58A39225D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="4500" windowWidth="21600" windowHeight="10980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="298">
   <si>
     <t>الموقع</t>
   </si>
@@ -981,10 +981,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1266,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D106"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.42578125" customWidth="1"/>
@@ -1289,1475 +1292,1044 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75">
+    <row r="2" spans="1:4" ht="31.5">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>294</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>295</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>296</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>174</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>175</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>176</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>15</v>
+        <v>88</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>254</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>255</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="1"/>
+        <v>256</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="6" spans="1:4" ht="15.75">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>45</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>127</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75">
+        <v>128</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="31.5">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>28</v>
+        <v>131</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>30</v>
+        <v>132</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75">
       <c r="A9" s="1" t="s">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>143</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>34</v>
+        <v>144</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75">
       <c r="A10" s="1" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>38</v>
+        <v>136</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>146</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>42</v>
+        <v>148</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>138</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>46</v>
+        <v>140</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75">
       <c r="A13" s="1" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="31.5">
+        <v>29</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.75">
       <c r="A14" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.75">
       <c r="A15" s="1" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>58</v>
+        <v>73</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.75">
       <c r="A16" s="1" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>60</v>
+        <v>259</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>62</v>
+        <v>260</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75">
       <c r="A17" s="1" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>66</v>
+        <v>14</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.75">
       <c r="A18" s="1" t="s">
-        <v>67</v>
+        <v>170</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>68</v>
+        <v>171</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>70</v>
+        <v>172</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75">
       <c r="A19" s="1" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15.75">
+        <v>112</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="31.5">
       <c r="A20" s="1" t="s">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>76</v>
+        <v>159</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>78</v>
+        <v>160</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.75">
       <c r="A21" s="1" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>82</v>
+        <v>61</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75">
       <c r="A22" s="1" t="s">
-        <v>83</v>
+        <v>186</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>84</v>
+        <v>187</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15.75">
+        <v>188</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="31.5">
       <c r="A23" s="1" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>42</v>
+        <v>100</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.75">
       <c r="A24" s="1" t="s">
-        <v>47</v>
+        <v>190</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>48</v>
+        <v>191</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>50</v>
+        <v>192</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="31.5">
       <c r="A25" s="1" t="s">
-        <v>51</v>
+        <v>222</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>54</v>
+        <v>224</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.75">
       <c r="A26" s="1" t="s">
-        <v>55</v>
+        <v>286</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>56</v>
+        <v>287</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>58</v>
+        <v>288</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75">
       <c r="A27" s="1" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>60</v>
+        <v>107</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15.75">
+        <v>108</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="31.5">
       <c r="A28" s="1" t="s">
-        <v>75</v>
+        <v>282</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>76</v>
+        <v>283</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>78</v>
+        <v>284</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15.75">
       <c r="A29" s="1" t="s">
-        <v>79</v>
+        <v>278</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>80</v>
+        <v>279</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="15.75">
+        <v>280</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="31.5">
       <c r="A30" s="1" t="s">
-        <v>63</v>
+        <v>166</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>64</v>
+        <v>167</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>66</v>
+        <v>168</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.75">
       <c r="A31" s="1" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>74</v>
+        <v>37</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75">
       <c r="A32" s="1" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>46</v>
+        <v>69</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.75">
       <c r="A33" s="1" t="s">
-        <v>86</v>
+        <v>202</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>87</v>
+        <v>203</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="31.5">
+        <v>204</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.75">
       <c r="A34" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="31.5">
+      <c r="A35" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B35" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D35" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15.75">
-      <c r="A35" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="31.5">
+    <row r="36" spans="1:4" ht="15.75">
       <c r="A36" s="1" t="s">
-        <v>98</v>
+        <v>274</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>99</v>
+        <v>275</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="15.75">
+        <v>276</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="31.5">
       <c r="A37" s="1" t="s">
-        <v>102</v>
+        <v>250</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>103</v>
+        <v>251</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>105</v>
+        <v>252</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.75">
       <c r="A38" s="1" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>109</v>
+        <v>81</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15.75">
       <c r="A39" s="1" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="31.5">
+        <v>124</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15.75">
       <c r="A40" s="1" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>117</v>
+        <v>164</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15.75">
       <c r="A41" s="1" t="s">
-        <v>118</v>
+        <v>242</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>119</v>
+        <v>243</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>121</v>
+        <v>244</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15.75">
       <c r="A42" s="1" t="s">
-        <v>122</v>
+        <v>246</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>123</v>
+        <v>247</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>125</v>
+        <v>248</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15.75">
       <c r="A43" s="1" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="31.5">
+        <v>77</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15.75">
       <c r="A44" s="1" t="s">
-        <v>130</v>
+        <v>206</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>131</v>
+        <v>207</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>133</v>
+        <v>208</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15.75">
       <c r="A45" s="1" t="s">
-        <v>134</v>
+        <v>238</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>135</v>
+        <v>239</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="15.75">
+        <v>240</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="31.5">
       <c r="A46" s="1" t="s">
-        <v>138</v>
+        <v>198</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>141</v>
+        <v>200</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15.75">
       <c r="A47" s="1" t="s">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>143</v>
+        <v>215</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>145</v>
+        <v>216</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15.75">
       <c r="A48" s="1" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>149</v>
+        <v>65</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="31.5">
       <c r="A49" s="1" t="s">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>151</v>
+        <v>271</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>153</v>
+        <v>272</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="31.5">
       <c r="A50" s="1" t="s">
-        <v>154</v>
+        <v>51</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>155</v>
+        <v>52</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>157</v>
+        <v>53</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="31.5">
       <c r="A51" s="1" t="s">
-        <v>158</v>
+        <v>218</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>161</v>
+        <v>220</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15.75">
       <c r="A52" s="1" t="s">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="31.5">
+        <v>120</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15.75">
       <c r="A53" s="1" t="s">
-        <v>166</v>
+        <v>31</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>167</v>
+        <v>32</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="15.75">
+        <v>33</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="31.5">
       <c r="A54" s="1" t="s">
-        <v>170</v>
+        <v>114</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>171</v>
+        <v>115</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>173</v>
+        <v>116</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15.75">
       <c r="A55" s="1" t="s">
-        <v>174</v>
+        <v>102</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>175</v>
+        <v>103</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>177</v>
+        <v>104</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="31.5">
       <c r="A56" s="1" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="15.75">
+        <v>152</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="18.75" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>182</v>
+        <v>39</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>183</v>
+        <v>40</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>185</v>
+        <v>41</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="15.75">
       <c r="A58" s="1" t="s">
-        <v>186</v>
+        <v>47</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>187</v>
+        <v>48</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>189</v>
+        <v>49</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15.75">
       <c r="A59" s="1" t="s">
-        <v>190</v>
+        <v>266</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>191</v>
+        <v>267</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="31.5">
+        <v>268</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="15.75">
       <c r="A60" s="1" t="s">
-        <v>194</v>
+        <v>4</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>195</v>
+        <v>5</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>197</v>
+        <v>6</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="31.5">
       <c r="A61" s="1" t="s">
-        <v>198</v>
+        <v>262</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>199</v>
+        <v>263</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>201</v>
+        <v>264</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15.75">
       <c r="A62" s="1" t="s">
-        <v>67</v>
+        <v>234</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>68</v>
+        <v>235</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="15.75">
+        <v>236</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="31.5">
       <c r="A63" s="1" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>205</v>
+        <v>180</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="15.75">
       <c r="A64" s="1" t="s">
-        <v>206</v>
+        <v>16</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>209</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="D64" s="2"/>
     </row>
     <row r="65" spans="1:4" ht="15.75">
       <c r="A65" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="31.5">
+      <c r="A66" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15.75">
+      <c r="A67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15.75">
+      <c r="A68" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B68" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C68" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D68" s="2" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="15.75">
-      <c r="A66" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="31.5">
-      <c r="A67" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="31.5">
-      <c r="A68" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="31.5">
+    <row r="69" spans="1:4" ht="15.75">
       <c r="A69" s="1" t="s">
-        <v>226</v>
+        <v>182</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>229</v>
+        <v>184</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.75">
       <c r="A70" s="1" t="s">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>231</v>
+        <v>291</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="15.75">
+        <v>292</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="31.5">
       <c r="A71" s="1" t="s">
-        <v>234</v>
+        <v>194</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>237</v>
+        <v>196</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15.75">
       <c r="A72" s="1" t="s">
-        <v>83</v>
+        <v>230</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>70</v>
+        <v>232</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="15.75">
       <c r="A73" s="1" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>42</v>
+        <v>85</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="15.75">
       <c r="A74" s="1" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>50</v>
+        <v>10</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="31.5">
       <c r="A75" s="1" t="s">
-        <v>51</v>
+        <v>226</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>52</v>
+        <v>227</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="15.75">
-      <c r="A76" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="15.75">
-      <c r="A77" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="15.75">
-      <c r="A78" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="15.75">
-      <c r="A79" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="15.75">
-      <c r="A80" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="15.75">
-      <c r="A81" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="15.75">
-      <c r="A82" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="15.75">
-      <c r="A83" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="15.75">
-      <c r="A84" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" ht="15.75">
-      <c r="A85" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" ht="31.5">
-      <c r="A86" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" ht="15.75">
-      <c r="A87" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="15.75">
-      <c r="A88" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" ht="31.5">
-      <c r="A89" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="15.75">
-      <c r="A90" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" ht="31.5">
-      <c r="A91" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="15.75">
-      <c r="A92" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="15.75">
-      <c r="A93" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="31.5">
-      <c r="A94" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="31.5">
-      <c r="A95" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" ht="15.75">
-      <c r="A96" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" ht="31.5">
-      <c r="A97" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="15.75">
-      <c r="A98" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="15.75">
-      <c r="A99" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="15.75">
-      <c r="A100" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="15.75">
-      <c r="A101" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" ht="15.75">
-      <c r="A102" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" ht="15.75">
-      <c r="A103" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" ht="31.5">
-      <c r="A104" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="15.75">
-      <c r="A105" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" ht="31.5">
-      <c r="A106" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>297</v>
+        <v>228</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>229</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D76">
+    <sortCondition ref="A2:A76"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
